--- a/templates/template_import_data_deletes.xlsx
+++ b/templates/template_import_data_deletes.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\source\repos\GanSoft\gansoft-resx\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B60278B1-29DF-4DDB-B723-DBAE9BA2ACD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10AD14E4-4C95-4A65-B75F-4C17476968AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="PesosCorporales" sheetId="1" r:id="rId1"/>
+    <sheet name="Eliminaciones" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -173,9 +173,9 @@
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="ID Electrónico" dataDxfId="5"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Práctico" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Fecha" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Razón" dataDxfId="0"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Técnico" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Comentario" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Razón" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Técnico" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Comentario" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
